--- a/jobs-template.xlsx
+++ b/jobs-template.xlsx
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="$#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -158,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -167,6 +168,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -200,6 +202,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -593,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -606,6 +609,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -657,6 +661,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>packing</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>miles</t>
         </is>
       </c>
     </row>
@@ -671,6 +680,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
+      <c r="K2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -683,6 +693,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
+      <c r="K3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -695,6 +706,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
+      <c r="K4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -707,6 +719,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
+      <c r="K5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -719,6 +732,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -731,6 +745,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -743,6 +758,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
+      <c r="K8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -755,6 +771,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="n"/>
+      <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -767,6 +784,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
+      <c r="K10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -779,6 +797,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
+      <c r="K11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -791,6 +810,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
+      <c r="K12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -803,6 +823,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -815,6 +836,7 @@
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -827,6 +849,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -839,6 +862,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
+      <c r="K16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -851,6 +875,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -863,6 +888,7 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
+      <c r="K18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -875,6 +901,7 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -887,6 +914,7 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -899,6 +927,7 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -911,6 +940,7 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
+      <c r="K22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -923,6 +953,7 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -935,6 +966,7 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
+      <c r="K24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -947,6 +979,7 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
+      <c r="K25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -959,6 +992,7 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="n"/>
+      <c r="K26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -971,6 +1005,7 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
+      <c r="K27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -983,6 +1018,7 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -995,6 +1031,7 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
+      <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1007,6 +1044,7 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
+      <c r="K30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1019,6 +1057,7 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
+      <c r="K31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1031,6 +1070,7 @@
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
+      <c r="K32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1043,6 +1083,7 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
+      <c r="K33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1055,6 +1096,7 @@
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
+      <c r="K34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1067,6 +1109,7 @@
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
+      <c r="K35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1079,6 +1122,7 @@
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
+      <c r="K36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1091,6 +1135,7 @@
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
+      <c r="K37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1103,6 +1148,7 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
+      <c r="K38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1115,6 +1161,7 @@
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
+      <c r="K39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1127,6 +1174,7 @@
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
+      <c r="K40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1139,6 +1187,7 @@
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
+      <c r="K41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1151,6 +1200,7 @@
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
+      <c r="K42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1163,6 +1213,7 @@
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
+      <c r="K43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1175,6 +1226,7 @@
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2" t="n"/>
+      <c r="K44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1187,6 +1239,7 @@
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2" t="n"/>
+      <c r="K45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -1199,6 +1252,7 @@
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="n"/>
+      <c r="K46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -1211,6 +1265,7 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="n"/>
+      <c r="K47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -1223,6 +1278,7 @@
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
+      <c r="K48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -1235,6 +1291,7 @@
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
       <c r="J49" s="2" t="n"/>
+      <c r="K49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -1247,6 +1304,7 @@
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="n"/>
+      <c r="K50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -1259,6 +1317,7 @@
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
+      <c r="K51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -1271,6 +1330,7 @@
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
+      <c r="K52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -1283,6 +1343,7 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
+      <c r="K53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -1295,6 +1356,7 @@
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
+      <c r="K54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -1307,6 +1369,7 @@
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2" t="n"/>
+      <c r="K55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -1319,6 +1382,7 @@
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
       <c r="J56" s="2" t="n"/>
+      <c r="K56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -1331,6 +1395,7 @@
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="n"/>
+      <c r="K57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -1343,6 +1408,7 @@
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2" t="n"/>
+      <c r="K58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -1355,6 +1421,7 @@
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
       <c r="J59" s="2" t="n"/>
+      <c r="K59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -1367,6 +1434,7 @@
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n"/>
       <c r="J60" s="2" t="n"/>
+      <c r="K60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -1379,6 +1447,7 @@
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
       <c r="J61" s="2" t="n"/>
+      <c r="K61" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -1411,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K54"/>
+  <dimension ref="B2:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1423,28 +1492,28 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>FLATIRONS MOVERS — HISTORICAL JOBS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>60 completed jobs, used to tune the pricing engine</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>What this is for</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>The engine's constants came from the prototype, not from data. Running your real jobs through it shows how many would have priced inside the quoted range. The target is 85–90%. Until that passes, every price the site quotes is a guess.</t>
         </is>
@@ -1452,14 +1521,14 @@
     </row>
     <row r="7"/>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>How to fill it in</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Fill the Jobs tab, one row per completed job. Yellow cells are the ones that matter most. Row 1 is the header — do not rename, reorder or delete those columns, and do not insert rows above it.</t>
         </is>
@@ -1467,501 +1536,549 @@
     </row>
     <row r="11"/>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Give me actual_hours if you possibly can</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>The two columns that matter most</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>This is the single most valuable column. Without it, throughput can only be inferred from how many jobs land inside the range — and that measure cannot pin it down: a job priced at its true throughput also lands inside the range for every value from 0.9× to 1.15× of it. That is a 28% blind spot. Recorded hours have no such ambiguity and give a direct read.</t>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>actual_hours — without it, throughput can only be inferred from how many jobs land inside the range, and that measure cannot pin it down: a job priced at its true throughput also lands inside the range for every value from 0.9x to 1.15x of it. Recorded hours have no such ambiguity.
+miles — the first tuning round found every one of the 60 invoices exceeding its labour estimate, by $101 at the very least and 17% of the bill at the median, with no job going the other way. The engine never modelled the $45 metro travel charge or the $1.15 per loaded mile beyond it. Mileage is what closes that gap.</t>
         </is>
       </c>
     </row>
     <row r="15"/>
     <row r="16"/>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Column by column</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="12" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Required?</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="B20" s="13" t="inlineStr">
+    <row r="23" ht="13" customHeight="1">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Your reference for the job. Only used to name rows in the report.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="B21" s="13" t="inlineStr">
+    <row r="24" ht="13" customHeight="1">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Either this</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Studio / 1 bed / 2 bed / 3+ bed. Seeds a typical inventory for that size.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="B22" s="13" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>items</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>or this</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>The real inventory, as Name:qty pairs separated by semicolons — e.g.  Sofa, 3-seat:1; Medium boxes:20.  Names must match the Catalogue tab exactly. Combine with size to start from the preset and adjust.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="B23" s="13" t="inlineStr">
+    <row r="26" ht="13" customHeight="1">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>movers</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>Strongly</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>2, 3 or 4. Defaults from size if blank, but the real crew size is better.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="B24" s="13" t="inlineStr">
+    <row r="27" ht="13" customHeight="1">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>actual_hours</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>Strongly</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Hours the crew actually billed. See the note above — this is the one that matters.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="B25" s="13" t="inlineStr">
+    <row r="28" ht="13" customHeight="1">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>invoice</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>The final amount the customer was charged, in dollars. Rows without it are skipped.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="13" customHeight="1">
-      <c r="B26" s="13" t="inlineStr">
+    <row r="29" ht="13" customHeight="1">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>from_floor</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Ground / 2nd / 3rd / 4th+ at the pickup. Blank means Ground.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="13" customHeight="1">
-      <c r="B27" s="13" t="inlineStr">
+    <row r="30" ht="13" customHeight="1">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>to_floor</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Same, at the drop-off.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="B28" s="13" t="inlineStr">
+    <row r="31" ht="13" customHeight="1">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>elevator</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>yes if a service elevator was reserved. Cancels both stair premiums.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="B29" s="13" t="inlineStr">
+    <row r="32" ht="13" customHeight="1">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>packing</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>yes if a packing crew went the day before.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="8" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Strongly</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Loaded miles from the pickup address to the drop-off. New — the first round showed every invoice exceeding its labour estimate, and travel is the missing charge. Odometer, dispatch log or Google Maps driving distance are all fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Two worked examples</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="15" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Do not copy these into the Jobs tab — it must contain only real jobs.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="16" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>items</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>movers</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>actual_hours</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>invoice</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>from_floor</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>to_floor</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J37" s="17" t="inlineStr">
         <is>
           <t>elevator</t>
         </is>
       </c>
-      <c r="K33" s="16" t="inlineStr">
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>packing</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="17" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>FM-1042</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>2 bed</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr"/>
-      <c r="E34" s="17" t="n">
+      <c r="D38" s="18" t="inlineStr"/>
+      <c r="E38" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F38" s="18" t="n">
         <v>4.75</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="G38" s="19" t="n">
         <v>995</v>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>Ground</t>
         </is>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>Ground</t>
         </is>
       </c>
-      <c r="J34" s="17" t="inlineStr">
+      <c r="J38" s="18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K34" s="17" t="inlineStr">
+      <c r="K38" s="18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="17" t="inlineStr">
+      <c r="L38" s="21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>FM-1043</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>1 bed</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>Upright piano:1; Bike:2</t>
         </is>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E39" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F39" s="18" t="n">
         <v>6.5</v>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="G39" s="19" t="n">
         <v>1480</v>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>Ground</t>
         </is>
       </c>
-      <c r="J35" s="17" t="inlineStr">
+      <c r="J39" s="18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K35" s="17" t="inlineStr">
+      <c r="K39" s="18" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="20" t="inlineStr">
+      <c r="L39" s="21" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>The second is a 1-bed that also had a piano and two bikes: the preset supplies the flat, the items column adds what the preset does not know about.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="8" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="21" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>Rows with an invoice</t>
         </is>
       </c>
-      <c r="C41" s="22">
+      <c r="C45" s="24">
         <f>COUNT(Jobs!F2:F61)</f>
         <v/>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D45" s="25" t="inlineStr">
         <is>
           <t>of 60 — the minimum a row needs to count</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="21" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>Rows with actual_hours</t>
         </is>
       </c>
-      <c r="C42" s="22">
+      <c r="C46" s="24">
         <f>COUNT(Jobs!E2:E61)</f>
         <v/>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D46" s="25" t="inlineStr">
         <is>
           <t>the column that resolves throughput directly</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="21" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>Rows with a size</t>
         </is>
       </c>
-      <c r="C43" s="22">
+      <c r="C47" s="24">
         <f>COUNTA(Jobs!B2:B61)</f>
         <v/>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D47" s="25" t="inlineStr">
         <is>
           <t>seeds the inventory from a preset</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="21" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Rows with an items list</t>
         </is>
       </c>
-      <c r="C44" s="22">
+      <c r="C48" s="24">
         <f>COUNTA(Jobs!C2:C61)</f>
         <v/>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>the real inventory, where you have it</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="21" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Rows with a crew size</t>
         </is>
       </c>
-      <c r="C45" s="22">
+      <c r="C49" s="24">
         <f>COUNT(Jobs!D2:D61)</f>
         <v/>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D49" s="25" t="inlineStr">
         <is>
           <t>better than letting it default</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="8" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Rows with miles</t>
+        </is>
+      </c>
+      <c r="C50" s="24">
+        <f>COUNT(Jobs!K2:K61)</f>
+        <v/>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>closes the gap the first round found</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>When it is filled in</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="9" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Export the Jobs tab on its own as CSV — File ▸ Save As ▸ CSV, with the Jobs tab selected; Excel writes only the active sheet. Name it jobs.csv, put it in the repo root, and run:</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="B51" s="24" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>npm run tune -- jobs.csv</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="20" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>Rows that cannot be used are reported by line number and skipped, so a partly finished sheet still gives a reading. Keep the file out of git — it is customer data.</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B14:F16"/>
     <mergeCell ref="B10:F11"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B53:F54"/>
+    <mergeCell ref="B58:F59"/>
+    <mergeCell ref="B14:F19"/>
     <mergeCell ref="B6:F7"/>
-    <mergeCell ref="B49:F50"/>
+    <mergeCell ref="B54:F55"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1984,43 +2101,43 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>CATALOGUE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Copy names into the items column exactly as written. A name the engine does not recognise is reported, not silently priced as zero.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>Volume units</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Handling</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Living room</t>
         </is>
@@ -2040,7 +2157,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="28" t="inlineStr"/>
+      <c r="B7" s="30" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Armchair</t>
@@ -2056,7 +2173,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr"/>
+      <c r="B8" s="30" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Coffee table</t>
@@ -2072,7 +2189,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr"/>
+      <c r="B9" s="30" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Bookcase, tall</t>
@@ -2088,7 +2205,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr"/>
+      <c r="B10" s="30" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>TV, 55 inch</t>
@@ -2097,14 +2214,14 @@
       <c r="D10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>TV crate +$40</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr"/>
+      <c r="B11" s="30" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Rug, rolled</t>
@@ -2120,7 +2237,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
@@ -2140,7 +2257,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr"/>
+      <c r="B13" s="30" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Refrigerator</t>
@@ -2156,7 +2273,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="28" t="inlineStr"/>
+      <c r="B14" s="30" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Dining table</t>
@@ -2172,7 +2289,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr"/>
+      <c r="B15" s="30" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Dining chairs</t>
@@ -2188,7 +2305,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr"/>
+      <c r="B16" s="30" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Bar stools</t>
@@ -2204,7 +2321,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Bedrooms</t>
         </is>
@@ -2224,7 +2341,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="28" t="inlineStr"/>
+      <c r="B18" s="30" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Bed, king</t>
@@ -2240,7 +2357,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="28" t="inlineStr"/>
+      <c r="B19" s="30" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Dresser</t>
@@ -2256,7 +2373,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="28" t="inlineStr"/>
+      <c r="B20" s="30" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Nightstand</t>
@@ -2272,7 +2389,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="28" t="inlineStr"/>
+      <c r="B21" s="30" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Wardrobe boxes</t>
@@ -2288,7 +2405,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="28" t="inlineStr"/>
+      <c r="B22" s="30" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Mattress only</t>
@@ -2304,7 +2421,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
@@ -2324,7 +2441,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="28" t="inlineStr"/>
+      <c r="B24" s="30" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Office chair</t>
@@ -2340,7 +2457,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="28" t="inlineStr"/>
+      <c r="B25" s="30" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Filing cabinet</t>
@@ -2356,7 +2473,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="28" t="inlineStr"/>
+      <c r="B26" s="30" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Monitor</t>
@@ -2372,7 +2489,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Garage &amp; misc</t>
         </is>
@@ -2392,7 +2509,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="28" t="inlineStr"/>
+      <c r="B28" s="30" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Bike</t>
@@ -2408,7 +2525,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="28" t="inlineStr"/>
+      <c r="B29" s="30" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Tool chest</t>
@@ -2424,7 +2541,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="28" t="inlineStr"/>
+      <c r="B30" s="30" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Upright piano</t>
@@ -2433,14 +2550,14 @@
       <c r="D30" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>Specialty +$180</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="28" t="inlineStr"/>
+      <c r="B31" s="30" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Treadmill</t>
@@ -2456,7 +2573,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="28" t="inlineStr"/>
+      <c r="B32" s="30" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Grill</t>
@@ -2472,45 +2589,45 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>Items in olive carry a surcharge on top of the labour.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="31" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>WHAT EACH SIZE ASSUMES</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>Choosing a size in the Jobs tab is shorthand for this inventory.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C38" s="29" t="inlineStr">
         <is>
           <t>Crew</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="D38" s="29" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="B39" s="28" t="inlineStr">
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>Studio</t>
         </is>
@@ -2520,15 +2637,15 @@
           <t>2 movers</t>
         </is>
       </c>
-      <c r="D39" s="33" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
         <is>
           <t>Bed, queen:1; Dresser:1; Medium boxes:10</t>
         </is>
       </c>
-      <c r="E39" s="34" t="n"/>
+      <c r="E39" s="36" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="28" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>1 bed</t>
         </is>
@@ -2538,15 +2655,15 @@
           <t>2 movers</t>
         </is>
       </c>
-      <c r="D40" s="33" t="inlineStr">
+      <c r="D40" s="35" t="inlineStr">
         <is>
           <t>Bed, queen:1; Sofa, 3-seat:1; Dresser:1; Medium boxes:14; Dining table:1; Dining chairs:2</t>
         </is>
       </c>
-      <c r="E40" s="34" t="n"/>
+      <c r="E40" s="36" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="B41" s="28" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>2 bed</t>
         </is>
@@ -2556,15 +2673,15 @@
           <t>3 movers</t>
         </is>
       </c>
-      <c r="D41" s="33" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>Bed, queen:1; Sofa, 3-seat:1; Dresser:2; Bookcase, tall:2; Medium boxes:22; Dining table:1; Dining chairs:4; TV, 55 inch:1</t>
         </is>
       </c>
-      <c r="E41" s="34" t="n"/>
+      <c r="E41" s="36" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>3+ bed</t>
         </is>
@@ -2574,12 +2691,12 @@
           <t>4 movers</t>
         </is>
       </c>
-      <c r="D42" s="33" t="inlineStr">
+      <c r="D42" s="35" t="inlineStr">
         <is>
           <t>Bed, king:1; Bed, queen:2; Sofa, 3-seat:1; Armchair:2; Dresser:3; Bookcase, tall:3; Medium boxes:34; Dining table:1; Dining chairs:6; TV, 55 inch:2; Refrigerator:1</t>
         </is>
       </c>
-      <c r="E42" s="34" t="n"/>
+      <c r="E42" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
